--- a/Assets/Resources/Excel sheets/Requests.xlsx
+++ b/Assets/Resources/Excel sheets/Requests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artem\Desktop\RMIT\RMIT sem 2 2026\GDS6\VANDERBILT\Assets\Resources\Excel sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A323A09-D335-4B23-B5BD-488FD9C8CE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B40CC32-8A5C-429D-8A7D-4506E57A598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3795" yWindow="2220" windowWidth="30570" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2055" windowWidth="30570" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>Reward</t>
   </si>
@@ -51,18 +51,12 @@
     <t>gold</t>
   </si>
   <si>
-    <t>blargh</t>
-  </si>
-  <si>
     <t>rep</t>
   </si>
   <si>
     <t>test2</t>
   </si>
   <si>
-    <t>bleh</t>
-  </si>
-  <si>
     <t>test4</t>
   </si>
   <si>
@@ -108,13 +102,205 @@
     <t>coal</t>
   </si>
   <si>
-    <t>huh</t>
-  </si>
-  <si>
     <t>test6</t>
   </si>
   <si>
-    <t>shrug</t>
+    <t xml:space="preserve">bi-monthy food restock </t>
+  </si>
+  <si>
+    <t>We are low on fuel for our smelters. this is hindering weapon production. Deliver us a new batch!</t>
+  </si>
+  <si>
+    <t>eckener</t>
+  </si>
+  <si>
+    <t>we need catering for the grand opening of our casino!</t>
+  </si>
+  <si>
+    <t>schwertlilie</t>
+  </si>
+  <si>
+    <t>we need more weapons our new recruits, help us protect the cirri!</t>
+  </si>
+  <si>
+    <t>Emergency Food Shipment</t>
+  </si>
+  <si>
+    <t>The residential district is running low on food.</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>Coal for the Factory</t>
+  </si>
+  <si>
+    <t>cirri</t>
+  </si>
+  <si>
+    <t>The factory boilers are running dangerously low.</t>
+  </si>
+  <si>
+    <t>Factory</t>
+  </si>
+  <si>
+    <t>Medical Supplies</t>
+  </si>
+  <si>
+    <t>medicine</t>
+  </si>
+  <si>
+    <t>The hospital is overwhelmed. We need medicine immediately.</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Fuel for the Airships</t>
+  </si>
+  <si>
+    <t>fuel</t>
+  </si>
+  <si>
+    <t>The docks cannot keep the airships running without fuel.</t>
+  </si>
+  <si>
+    <t>Airship Dock</t>
+  </si>
+  <si>
+    <t>Weapons for the Military</t>
+  </si>
+  <si>
+    <t>The military is requesting additional weapons.</t>
+  </si>
+  <si>
+    <t>unrest</t>
+  </si>
+  <si>
+    <t>Military</t>
+  </si>
+  <si>
+    <t>Machine Parts</t>
+  </si>
+  <si>
+    <t>machinery</t>
+  </si>
+  <si>
+    <t>The factory requires replacement machinery.</t>
+  </si>
+  <si>
+    <t>Ore Shipment</t>
+  </si>
+  <si>
+    <t>ore</t>
+  </si>
+  <si>
+    <t>The mine requires additional supplies to continue production.</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>Mine</t>
+  </si>
+  <si>
+    <t>Medicine for the District</t>
+  </si>
+  <si>
+    <t>The hospital has reported a sudden increase in patients.</t>
+  </si>
+  <si>
+    <t>Food for Workers</t>
+  </si>
+  <si>
+    <t>The workers have not received their full rations this week.</t>
+  </si>
+  <si>
+    <t>Coal for the Warehouse</t>
+  </si>
+  <si>
+    <t>The warehouse requires coal to keep its machinery running.</t>
+  </si>
+  <si>
+    <t>Warehouse</t>
+  </si>
+  <si>
+    <t>Military Equipment</t>
+  </si>
+  <si>
+    <t>The military requires additional equipment for patrols.</t>
+  </si>
+  <si>
+    <t>Machinery for the Mine</t>
+  </si>
+  <si>
+    <t>The mining equipment is failing faster than expected.</t>
+  </si>
+  <si>
+    <t>Fuel for the Government</t>
+  </si>
+  <si>
+    <t>The government requires fuel for emergency generators.</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Luxury Food Delivery</t>
+  </si>
+  <si>
+    <t>The market has received an order for premium food.</t>
+  </si>
+  <si>
+    <t>pollution</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Emergency Coal Reserve</t>
+  </si>
+  <si>
+    <t>The resource depot needs an emergency coal reserve.</t>
+  </si>
+  <si>
+    <t>ResourceDepot</t>
+  </si>
+  <si>
+    <t>Revolutionary Supplies</t>
+  </si>
+  <si>
+    <t>Keep this shipment quiet. The government must not know about it.</t>
+  </si>
+  <si>
+    <t>Factory Machinery</t>
+  </si>
+  <si>
+    <t>Production has stopped. The factory needs machinery.</t>
+  </si>
+  <si>
+    <t>Ore for Construction</t>
+  </si>
+  <si>
+    <t>The government has ordered ore for a new construction project.</t>
+  </si>
+  <si>
+    <t>Disease Relief</t>
+  </si>
+  <si>
+    <t>The hospital needs medicine before the disease spreads further.</t>
+  </si>
+  <si>
+    <t>Fuel for the Resistance</t>
+  </si>
+  <si>
+    <t>The residential district needs fuel for its generators.</t>
+  </si>
+  <si>
+    <t>LocationType</t>
   </si>
 </sst>
 </file>
@@ -185,11 +371,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -474,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="23.42578125" customWidth="1"/>
@@ -487,50 +670,55 @@
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
     <col min="11" max="11" width="11.85546875" customWidth="1"/>
     <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" customWidth="1"/>
+    <col min="14" max="14" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="60" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="60" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -538,7 +726,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>60</v>
@@ -553,10 +741,10 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
         <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
       </c>
       <c r="J2">
         <v>5</v>
@@ -567,16 +755,19 @@
       <c r="L2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3">
         <v>40</v>
@@ -591,10 +782,10 @@
         <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -605,17 +796,20 @@
       <c r="L3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>20</v>
@@ -630,10 +824,10 @@
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -644,13 +838,19 @@
       <c r="L5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>50</v>
@@ -665,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -676,17 +876,26 @@
       <c r="L6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>50</v>
       </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
       <c r="F7">
         <v>100</v>
       </c>
@@ -694,7 +903,7 @@
         <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -705,48 +914,835 @@
       <c r="L7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="M7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>75</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>40</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8">
+        <v>-5</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>-3</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10">
+        <v>90</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>-3</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>120</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13">
+        <v>75</v>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13">
+        <v>-4</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>90</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14">
+        <v>-5</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15">
+        <v>110</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
+      </c>
+      <c r="H15" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15">
+        <v>-8</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16">
+        <v>65</v>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16">
+        <v>-4</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
+        <v>45</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17">
+        <v>70</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17">
+        <v>-2</v>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18">
+        <v>60</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19">
+        <v>95</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19">
+        <v>-5</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>55</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>85</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <v>-3</v>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>1</v>
+      </c>
+      <c r="M20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>150</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="H21" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" t="s">
+        <v>76</v>
+      </c>
+      <c r="J21">
+        <v>2</v>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22">
+        <v>120</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22">
+        <v>140</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22" t="s">
+        <v>76</v>
+      </c>
+      <c r="J22">
+        <v>8</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23">
+        <v>60</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23">
+        <v>200</v>
+      </c>
+      <c r="G23">
+        <v>6</v>
+      </c>
+      <c r="H23" t="s">
+        <v>82</v>
+      </c>
+      <c r="I23" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23">
+        <v>8</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24">
+        <v>70</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24">
+        <v>160</v>
+      </c>
+      <c r="G24">
+        <v>9</v>
+      </c>
+      <c r="H24" t="s">
+        <v>84</v>
+      </c>
+      <c r="I24" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24">
+        <v>6</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25">
+        <v>150</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25">
+        <v>130</v>
+      </c>
+      <c r="G25">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" t="s">
+        <v>76</v>
+      </c>
+      <c r="J25">
+        <v>7</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+      <c r="M25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26">
+        <v>80</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26">
+        <v>175</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>-12</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27">
+        <v>150</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+      <c r="H27" t="s">
+        <v>90</v>
+      </c>
+      <c r="I27" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27">
+        <v>10</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/Assets/Resources/Excel sheets/Requests.xlsx
+++ b/Assets/Resources/Excel sheets/Requests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artem\Desktop\RMIT\RMIT sem 2 2026\GDS6\VANDERBILT\Assets\Resources\Excel sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B40CC32-8A5C-429D-8A7D-4506E57A598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B4A634-4E1E-4B82-A784-0C3D52BFB263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2055" windowWidth="30570" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,6 +325,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -371,10 +379,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -657,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="23.42578125" customWidth="1"/>
@@ -674,7 +688,7 @@
     <col min="14" max="14" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -718,7 +732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="60" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="60" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -737,8 +751,8 @@
       <c r="F2">
         <v>25</v>
       </c>
-      <c r="G2">
-        <v>5</v>
+      <c r="G2" s="3">
+        <v>300</v>
       </c>
       <c r="H2" t="s">
         <v>26</v>
@@ -759,7 +773,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -778,8 +792,8 @@
       <c r="F3">
         <v>50</v>
       </c>
-      <c r="G3">
-        <v>6</v>
+      <c r="G3" s="3">
+        <v>360</v>
       </c>
       <c r="H3" t="s">
         <v>27</v>
@@ -800,8 +814,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -820,8 +834,8 @@
       <c r="F5">
         <v>75</v>
       </c>
-      <c r="G5">
-        <v>8</v>
+      <c r="G5" s="3">
+        <v>480</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -842,7 +856,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -861,8 +875,8 @@
       <c r="F6">
         <v>100</v>
       </c>
-      <c r="G6">
-        <v>8</v>
+      <c r="G6" s="3">
+        <v>480</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
@@ -880,7 +894,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -899,8 +913,8 @@
       <c r="F7">
         <v>100</v>
       </c>
-      <c r="G7">
-        <v>8</v>
+      <c r="G7" s="3">
+        <v>480</v>
       </c>
       <c r="H7" t="s">
         <v>31</v>
@@ -917,8 +931,10 @@
       <c r="M7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -937,8 +953,8 @@
       <c r="F8">
         <v>40</v>
       </c>
-      <c r="G8">
-        <v>6</v>
+      <c r="G8" s="3">
+        <v>360</v>
       </c>
       <c r="H8" t="s">
         <v>33</v>
@@ -958,8 +974,10 @@
       <c r="M8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -978,8 +996,8 @@
       <c r="F9">
         <v>80</v>
       </c>
-      <c r="G9">
-        <v>7</v>
+      <c r="G9" s="3">
+        <v>420</v>
       </c>
       <c r="H9" t="s">
         <v>37</v>
@@ -999,8 +1017,10 @@
       <c r="M9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1019,8 +1039,8 @@
       <c r="F10">
         <v>90</v>
       </c>
-      <c r="G10">
-        <v>5</v>
+      <c r="G10" s="3">
+        <v>300</v>
       </c>
       <c r="H10" t="s">
         <v>41</v>
@@ -1040,8 +1060,10 @@
       <c r="M10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1060,8 +1082,8 @@
       <c r="F11">
         <v>100</v>
       </c>
-      <c r="G11">
-        <v>8</v>
+      <c r="G11" s="3">
+        <v>480</v>
       </c>
       <c r="H11" t="s">
         <v>46</v>
@@ -1081,8 +1103,10 @@
       <c r="M11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1101,8 +1125,8 @@
       <c r="F12">
         <v>120</v>
       </c>
-      <c r="G12">
-        <v>7</v>
+      <c r="G12" s="3">
+        <v>420</v>
       </c>
       <c r="H12" t="s">
         <v>49</v>
@@ -1122,8 +1146,10 @@
       <c r="M12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1142,8 +1168,8 @@
       <c r="F13">
         <v>75</v>
       </c>
-      <c r="G13">
-        <v>6</v>
+      <c r="G13" s="3">
+        <v>360</v>
       </c>
       <c r="H13" t="s">
         <v>54</v>
@@ -1163,8 +1189,10 @@
       <c r="M13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -1183,8 +1211,8 @@
       <c r="F14">
         <v>90</v>
       </c>
-      <c r="G14">
-        <v>9</v>
+      <c r="G14" s="3">
+        <v>540</v>
       </c>
       <c r="H14" t="s">
         <v>57</v>
@@ -1204,8 +1232,10 @@
       <c r="M14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1224,8 +1254,8 @@
       <c r="F15">
         <v>110</v>
       </c>
-      <c r="G15">
-        <v>4</v>
+      <c r="G15" s="3">
+        <v>240</v>
       </c>
       <c r="H15" t="s">
         <v>61</v>
@@ -1245,8 +1275,10 @@
       <c r="M15" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -1265,8 +1297,8 @@
       <c r="F16">
         <v>65</v>
       </c>
-      <c r="G16">
-        <v>8</v>
+      <c r="G16" s="3">
+        <v>480</v>
       </c>
       <c r="H16" t="s">
         <v>63</v>
@@ -1286,8 +1318,10 @@
       <c r="M16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -1306,8 +1340,8 @@
       <c r="F17">
         <v>70</v>
       </c>
-      <c r="G17">
-        <v>5</v>
+      <c r="G17" s="3">
+        <v>300</v>
       </c>
       <c r="H17" t="s">
         <v>65</v>
@@ -1327,8 +1361,10 @@
       <c r="M17" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -1347,8 +1383,8 @@
       <c r="F18">
         <v>60</v>
       </c>
-      <c r="G18">
-        <v>5</v>
+      <c r="G18" s="3">
+        <v>300</v>
       </c>
       <c r="H18" t="s">
         <v>68</v>
@@ -1368,8 +1404,10 @@
       <c r="M18" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -1388,8 +1426,8 @@
       <c r="F19">
         <v>95</v>
       </c>
-      <c r="G19">
-        <v>10</v>
+      <c r="G19" s="3">
+        <v>600</v>
       </c>
       <c r="H19" t="s">
         <v>70</v>
@@ -1409,8 +1447,10 @@
       <c r="M19" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -1429,8 +1469,8 @@
       <c r="F20">
         <v>85</v>
       </c>
-      <c r="G20">
-        <v>7</v>
+      <c r="G20" s="3">
+        <v>420</v>
       </c>
       <c r="H20" t="s">
         <v>72</v>
@@ -1450,8 +1490,10 @@
       <c r="M20" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -1470,8 +1512,8 @@
       <c r="F21">
         <v>150</v>
       </c>
-      <c r="G21">
-        <v>5</v>
+      <c r="G21" s="3">
+        <v>300</v>
       </c>
       <c r="H21" t="s">
         <v>75</v>
@@ -1491,8 +1533,10 @@
       <c r="M21" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>78</v>
       </c>
@@ -1511,8 +1555,8 @@
       <c r="F22">
         <v>140</v>
       </c>
-      <c r="G22">
-        <v>10</v>
+      <c r="G22" s="3">
+        <v>600</v>
       </c>
       <c r="H22" t="s">
         <v>79</v>
@@ -1532,8 +1576,10 @@
       <c r="M22" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
@@ -1552,8 +1598,8 @@
       <c r="F23">
         <v>200</v>
       </c>
-      <c r="G23">
-        <v>6</v>
+      <c r="G23" s="3">
+        <v>360</v>
       </c>
       <c r="H23" t="s">
         <v>82</v>
@@ -1573,8 +1619,10 @@
       <c r="M23" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -1593,8 +1641,8 @@
       <c r="F24">
         <v>160</v>
       </c>
-      <c r="G24">
-        <v>9</v>
+      <c r="G24" s="3">
+        <v>540</v>
       </c>
       <c r="H24" t="s">
         <v>84</v>
@@ -1614,8 +1662,10 @@
       <c r="M24" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>85</v>
       </c>
@@ -1634,8 +1684,8 @@
       <c r="F25">
         <v>130</v>
       </c>
-      <c r="G25">
-        <v>12</v>
+      <c r="G25" s="3">
+        <v>720</v>
       </c>
       <c r="H25" t="s">
         <v>86</v>
@@ -1655,8 +1705,10 @@
       <c r="M25" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>87</v>
       </c>
@@ -1675,8 +1727,8 @@
       <c r="F26">
         <v>175</v>
       </c>
-      <c r="G26">
-        <v>8</v>
+      <c r="G26" s="3">
+        <v>480</v>
       </c>
       <c r="H26" t="s">
         <v>88</v>
@@ -1696,8 +1748,10 @@
       <c r="M26" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -1716,8 +1770,8 @@
       <c r="F27">
         <v>150</v>
       </c>
-      <c r="G27">
-        <v>6</v>
+      <c r="G27" s="3">
+        <v>360</v>
       </c>
       <c r="H27" t="s">
         <v>90</v>
@@ -1737,12 +1791,29 @@
       <c r="M27" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+    </row>
     <row r="33" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="60" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1774,5 +1845,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>